--- a/saad-digital-marketing/data/saad-digi-marketing-dta.xlsx
+++ b/saad-digital-marketing/data/saad-digi-marketing-dta.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\Chris Llones - 2024\GoogleDrive\VSU\viserdac\viserdac-data-analysis\20260503-pening-saad-digital-marketing-adoption\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\viser\OneDrive\Dokumen\Github repository\data-consultation-2026\saad-digital-marketing\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{777C4AE1-91A4-46E5-BD38-B66F0DB7E5E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D08DCF22-2150-4D87-B170-2C64C4EFCECF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{6C9933B8-D739-4C2C-BD08-E89F383740DE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{6C9933B8-D739-4C2C-BD08-E89F383740DE}"/>
   </bookViews>
   <sheets>
     <sheet name="raw_data" sheetId="4" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4143" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4143" uniqueCount="302">
   <si>
     <t>Respondent No.</t>
   </si>
@@ -883,15 +883,6 @@
     <t>factor</t>
   </si>
   <si>
-    <t>Technological barriers</t>
-  </si>
-  <si>
-    <t>Organizational barriers</t>
-  </si>
-  <si>
-    <t>Environmental barriers</t>
-  </si>
-  <si>
     <t>Digital marketing adoption</t>
   </si>
   <si>
@@ -944,6 +935,18 @@
   </si>
   <si>
     <t xml:space="preserve">Our enterprise interacts with customers online by  responding to comments, messages, or feedback on digital platforms. </t>
+  </si>
+  <si>
+    <t>Limited digital infrastructure</t>
+  </si>
+  <si>
+    <t>Technological complexity</t>
+  </si>
+  <si>
+    <t>Lack of managerial support</t>
+  </si>
+  <si>
+    <t>Limited government support</t>
   </si>
 </sst>
 </file>
@@ -1422,12 +1425,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA160F2E-15E0-4DCB-9867-595089422D9C}">
   <dimension ref="A1:AM109"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="38" max="38" width="53.88671875" customWidth="1"/>
+    <col min="38" max="38" width="53.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1546,7 +1549,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1662,7 +1665,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="3" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1778,7 +1781,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="4" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1894,7 +1897,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="5" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2010,7 +2013,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="6" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2126,7 +2129,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="7" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2242,7 +2245,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="8" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2358,7 +2361,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="9" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2474,7 +2477,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="10" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2590,7 +2593,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="11" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2706,7 +2709,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="12" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2822,7 +2825,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="13" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2938,7 +2941,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="14" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -3054,7 +3057,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="15" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -3170,7 +3173,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="16" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -3286,7 +3289,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="17" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -3402,7 +3405,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="18" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -3518,7 +3521,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="19" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -3634,7 +3637,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="20" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -3750,7 +3753,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="21" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -3866,7 +3869,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="22" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -3982,7 +3985,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="23" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -4098,7 +4101,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="24" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -4217,7 +4220,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="25" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -4336,7 +4339,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="26" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -4455,7 +4458,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="27" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -4574,7 +4577,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="28" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -4690,7 +4693,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="29" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -4806,7 +4809,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="30" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -4922,7 +4925,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="31" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -5038,7 +5041,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="32" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -5154,7 +5157,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="33" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -5270,7 +5273,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="34" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
@@ -5386,7 +5389,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="35" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
@@ -5502,7 +5505,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="36" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
@@ -5618,7 +5621,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="37" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -5734,7 +5737,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="38" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
@@ -5850,7 +5853,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="39" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
@@ -5966,7 +5969,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="40" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
@@ -6082,7 +6085,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="41" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
@@ -6198,7 +6201,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="42" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
@@ -6317,7 +6320,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="43" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
@@ -6436,7 +6439,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="44" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
@@ -6552,7 +6555,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="45" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
@@ -6668,7 +6671,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="46" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
@@ -6784,7 +6787,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="47" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
@@ -6900,7 +6903,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="48" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
@@ -7016,7 +7019,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="49" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
@@ -7132,7 +7135,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="50" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
@@ -7248,7 +7251,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="51" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
@@ -7364,7 +7367,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="52" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
@@ -7483,7 +7486,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="53" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
@@ -7602,7 +7605,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="54" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
@@ -7718,7 +7721,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="55" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
@@ -7834,7 +7837,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="56" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>55</v>
       </c>
@@ -7950,7 +7953,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="57" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>56</v>
       </c>
@@ -8066,7 +8069,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="58" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>57</v>
       </c>
@@ -8182,7 +8185,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="59" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>58</v>
       </c>
@@ -8298,7 +8301,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="60" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
@@ -8414,7 +8417,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="61" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>60</v>
       </c>
@@ -8530,7 +8533,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="62" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>61</v>
       </c>
@@ -8646,7 +8649,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="63" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>62</v>
       </c>
@@ -8762,7 +8765,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="64" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>63</v>
       </c>
@@ -8878,7 +8881,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="65" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>64</v>
       </c>
@@ -8994,7 +8997,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="66" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>65</v>
       </c>
@@ -9110,7 +9113,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="67" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>66</v>
       </c>
@@ -9226,7 +9229,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="68" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>67</v>
       </c>
@@ -9342,7 +9345,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="69" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>68</v>
       </c>
@@ -9458,7 +9461,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="70" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>69</v>
       </c>
@@ -9574,7 +9577,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="71" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>70</v>
       </c>
@@ -9690,7 +9693,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="72" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>71</v>
       </c>
@@ -9806,7 +9809,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="73" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>72</v>
       </c>
@@ -9922,7 +9925,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="74" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>73</v>
       </c>
@@ -10038,7 +10041,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="75" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>74</v>
       </c>
@@ -10154,7 +10157,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="76" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>75</v>
       </c>
@@ -10270,7 +10273,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="77" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>76</v>
       </c>
@@ -10386,7 +10389,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="78" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>77</v>
       </c>
@@ -10502,7 +10505,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="79" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>78</v>
       </c>
@@ -10618,7 +10621,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="80" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>79</v>
       </c>
@@ -10737,7 +10740,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="81" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>80</v>
       </c>
@@ -10856,7 +10859,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="82" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>81</v>
       </c>
@@ -10972,7 +10975,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="83" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>82</v>
       </c>
@@ -11088,7 +11091,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="84" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>83</v>
       </c>
@@ -11204,7 +11207,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="85" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>84</v>
       </c>
@@ -11320,7 +11323,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="86" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>85</v>
       </c>
@@ -11436,7 +11439,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="87" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>86</v>
       </c>
@@ -11552,7 +11555,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="88" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>87</v>
       </c>
@@ -11668,7 +11671,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="89" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>88</v>
       </c>
@@ -11784,7 +11787,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="90" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>89</v>
       </c>
@@ -11900,7 +11903,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="91" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>90</v>
       </c>
@@ -12016,7 +12019,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="92" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>91</v>
       </c>
@@ -12132,7 +12135,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="93" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>92</v>
       </c>
@@ -12248,7 +12251,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="94" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>93</v>
       </c>
@@ -12364,7 +12367,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="95" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>94</v>
       </c>
@@ -12480,7 +12483,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="96" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>95</v>
       </c>
@@ -12599,7 +12602,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="97" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>96</v>
       </c>
@@ -12718,7 +12721,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="98" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>97</v>
       </c>
@@ -12834,7 +12837,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="99" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>98</v>
       </c>
@@ -12950,7 +12953,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="100" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>99</v>
       </c>
@@ -13066,7 +13069,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="101" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>100</v>
       </c>
@@ -13182,7 +13185,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="102" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>101</v>
       </c>
@@ -13298,7 +13301,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="103" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>102</v>
       </c>
@@ -13414,7 +13417,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="104" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>103</v>
       </c>
@@ -13530,7 +13533,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="105" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>104</v>
       </c>
@@ -13646,7 +13649,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="106" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>105</v>
       </c>
@@ -13762,7 +13765,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="107" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>106</v>
       </c>
@@ -13878,7 +13881,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="108" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>107</v>
       </c>
@@ -13994,7 +13997,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="109" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>108</v>
       </c>
@@ -14118,15 +14121,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEC0CBDA-3B93-40AA-9954-2AC3A7BE968C}">
   <dimension ref="A1:C20"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="133" style="16" customWidth="1"/>
-    <col min="2" max="2" width="18.77734375" style="16" customWidth="1"/>
-    <col min="3" max="3" width="41.6640625" style="16" customWidth="1"/>
-    <col min="4" max="16384" width="8.88671875" style="16"/>
+    <col min="2" max="2" width="18.7109375" style="16" customWidth="1"/>
+    <col min="3" max="3" width="41.7109375" style="16" customWidth="1"/>
+    <col min="4" max="16384" width="8.85546875" style="16"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
         <v>277</v>
       </c>
@@ -14137,213 +14140,213 @@
         <v>279</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="B2" s="16" t="s">
         <v>8</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>280</v>
+        <v>298</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="B3" s="16" t="s">
         <v>9</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>280</v>
+        <v>298</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="B4" s="16" t="s">
         <v>10</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>280</v>
+        <v>298</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B5" s="16" t="s">
         <v>11</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>280</v>
+        <v>299</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="17" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B6" s="16" t="s">
         <v>12</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>280</v>
+        <v>299</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="17" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="B7" s="16" t="s">
         <v>13</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>280</v>
+        <v>299</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="B8" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>281</v>
+        <v>203</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="B9" s="16" t="s">
         <v>15</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>281</v>
+        <v>203</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="B10" s="16" t="s">
         <v>16</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>281</v>
+        <v>203</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B11" s="16" t="s">
         <v>17</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>281</v>
+        <v>300</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="B12" s="16" t="s">
         <v>18</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>281</v>
+        <v>300</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="17" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="B13" s="16" t="s">
         <v>19</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>281</v>
+        <v>300</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B14" s="16" t="s">
         <v>20</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>282</v>
+        <v>301</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="B15" s="16" t="s">
         <v>21</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>282</v>
+        <v>301</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="B16" s="16" t="s">
         <v>22</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>282</v>
+        <v>301</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="17" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B17" s="16" t="s">
         <v>23</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="17" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="B18" s="16" t="s">
         <v>24</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="17" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="B19" s="16" t="s">
         <v>25</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="B20" s="16" t="s">
         <v>26</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
     </row>
   </sheetData>
@@ -14354,17 +14357,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20B19222-BD5E-4C89-A3BF-6B5AAE966D6F}">
   <dimension ref="A1:AM109"/>
-  <sheetFormatPr defaultRowHeight="10.199999999999999" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="11.25" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="6" width="10.77734375" style="5" customWidth="1"/>
-    <col min="7" max="7" width="23.88671875" style="5" customWidth="1"/>
-    <col min="8" max="18" width="10.77734375" style="5" customWidth="1"/>
-    <col min="19" max="37" width="5.77734375" style="5" customWidth="1"/>
-    <col min="38" max="39" width="10.77734375" style="5" customWidth="1"/>
-    <col min="40" max="16384" width="8.88671875" style="5"/>
+    <col min="1" max="6" width="10.7109375" style="5" customWidth="1"/>
+    <col min="7" max="7" width="23.85546875" style="5" customWidth="1"/>
+    <col min="8" max="18" width="10.7109375" style="5" customWidth="1"/>
+    <col min="19" max="37" width="5.7109375" style="5" customWidth="1"/>
+    <col min="38" max="39" width="10.7109375" style="5" customWidth="1"/>
+    <col min="40" max="16384" width="8.85546875" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39" s="2" customFormat="1" ht="40.799999999999997" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:39" s="2" customFormat="1" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -14483,7 +14486,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:39" ht="71.400000000000006" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:39" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -14600,7 +14603,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="3" spans="1:39" ht="40.799999999999997" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:39" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <f>A2+1</f>
         <v>2</v>
@@ -14718,7 +14721,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="4" spans="1:39" ht="40.799999999999997" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:39" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <f>A3+1</f>
         <v>3</v>
@@ -14836,7 +14839,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="5" spans="1:39" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:39" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <f t="shared" ref="A5:A30" si="0">A4+1</f>
         <v>4</v>
@@ -14954,7 +14957,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="6" spans="1:39" ht="40.799999999999997" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:39" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -15072,7 +15075,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="7" spans="1:39" ht="40.799999999999997" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:39" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -15190,7 +15193,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="8" spans="1:39" ht="51" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:39" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -15308,7 +15311,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="9" spans="1:39" ht="51" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:39" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -15426,7 +15429,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="10" spans="1:39" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:39" ht="51" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -15544,7 +15547,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="11" spans="1:39" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:39" ht="51" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -15662,7 +15665,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="12" spans="1:39" ht="40.799999999999997" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:39" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -15780,7 +15783,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="13" spans="1:39" ht="40.799999999999997" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:39" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -15898,7 +15901,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="14" spans="1:39" ht="40.799999999999997" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:39" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -16016,7 +16019,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="15" spans="1:39" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:39" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -16134,7 +16137,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="16" spans="1:39" ht="61.2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:39" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -16252,7 +16255,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="17" spans="1:39" ht="61.2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:39" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -16370,7 +16373,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="18" spans="1:39" ht="40.799999999999997" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:39" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -16488,7 +16491,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="19" spans="1:39" ht="40.799999999999997" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:39" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -16606,7 +16609,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="20" spans="1:39" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:39" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -16724,7 +16727,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="21" spans="1:39" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:39" ht="45" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -16842,7 +16845,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="22" spans="1:39" ht="61.2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:39" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -16960,7 +16963,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="23" spans="1:39" ht="61.2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:39" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -17078,7 +17081,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="24" spans="1:39" ht="40.799999999999997" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:39" ht="45" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -17198,7 +17201,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="25" spans="1:39" ht="40.799999999999997" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:39" ht="45" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -17318,7 +17321,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="26" spans="1:39" ht="51" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:39" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -17438,7 +17441,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="27" spans="1:39" ht="51" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:39" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -17558,7 +17561,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="28" spans="1:39" ht="40.799999999999997" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:39" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <f>A27+1</f>
         <v>27</v>
@@ -17676,7 +17679,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="29" spans="1:39" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:39" ht="45" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -17794,7 +17797,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="30" spans="1:39" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:39" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -17912,7 +17915,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="31" spans="1:39" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:39" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <f>A30+1</f>
         <v>30</v>
@@ -18030,7 +18033,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="32" spans="1:39" ht="40.799999999999997" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:39" ht="45" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <f t="shared" ref="A32:A54" si="1">A31+1</f>
         <v>31</v>
@@ -18148,7 +18151,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="33" spans="1:39" ht="40.799999999999997" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:39" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <f t="shared" si="1"/>
         <v>32</v>
@@ -18266,7 +18269,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="34" spans="1:39" ht="40.799999999999997" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:39" ht="45" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <f t="shared" si="1"/>
         <v>33</v>
@@ -18384,7 +18387,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="35" spans="1:39" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:39" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <f t="shared" si="1"/>
         <v>34</v>
@@ -18502,7 +18505,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="36" spans="1:39" ht="40.799999999999997" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:39" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <f t="shared" si="1"/>
         <v>35</v>
@@ -18620,7 +18623,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="37" spans="1:39" ht="40.799999999999997" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:39" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
         <f t="shared" si="1"/>
         <v>36</v>
@@ -18738,7 +18741,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="38" spans="1:39" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:39" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
         <f t="shared" si="1"/>
         <v>37</v>
@@ -18856,7 +18859,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="39" spans="1:39" ht="40.799999999999997" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:39" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
         <f t="shared" si="1"/>
         <v>38</v>
@@ -18974,7 +18977,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="40" spans="1:39" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:39" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
         <f t="shared" si="1"/>
         <v>39</v>
@@ -19092,7 +19095,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="41" spans="1:39" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:39" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
         <f t="shared" si="1"/>
         <v>40</v>
@@ -19210,7 +19213,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="42" spans="1:39" ht="40.799999999999997" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:39" ht="45" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
         <f t="shared" si="1"/>
         <v>41</v>
@@ -19330,7 +19333,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="43" spans="1:39" ht="40.799999999999997" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:39" ht="45" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
         <f t="shared" si="1"/>
         <v>42</v>
@@ -19450,7 +19453,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="44" spans="1:39" ht="51" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:39" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
         <f t="shared" si="1"/>
         <v>43</v>
@@ -19568,7 +19571,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="45" spans="1:39" ht="51" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:39" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
         <f t="shared" si="1"/>
         <v>44</v>
@@ -19686,7 +19689,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="46" spans="1:39" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:39" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
         <f t="shared" si="1"/>
         <v>45</v>
@@ -19804,7 +19807,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="47" spans="1:39" ht="40.799999999999997" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:39" ht="45" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <f t="shared" si="1"/>
         <v>46</v>
@@ -19922,7 +19925,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="48" spans="1:39" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:39" ht="45" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <f t="shared" si="1"/>
         <v>47</v>
@@ -20040,7 +20043,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="49" spans="1:39" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:39" ht="45" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
         <f t="shared" si="1"/>
         <v>48</v>
@@ -20158,7 +20161,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="50" spans="1:39" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:39" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
         <f t="shared" si="1"/>
         <v>49</v>
@@ -20276,7 +20279,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="51" spans="1:39" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:39" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
         <f>A50+1</f>
         <v>50</v>
@@ -20394,7 +20397,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="52" spans="1:39" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:39" ht="45" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
         <f t="shared" si="1"/>
         <v>51</v>
@@ -20514,7 +20517,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="53" spans="1:39" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:39" ht="45" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
         <f t="shared" si="1"/>
         <v>52</v>
@@ -20634,7 +20637,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="54" spans="1:39" ht="66" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:39" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
         <f t="shared" si="1"/>
         <v>53</v>
@@ -20752,7 +20755,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="55" spans="1:39" ht="66" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:39" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A55" s="3">
         <f>A54+1</f>
         <v>54</v>
@@ -20870,7 +20873,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="56" spans="1:39" ht="40.799999999999997" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:39" ht="45" x14ac:dyDescent="0.25">
       <c r="A56" s="3">
         <f t="shared" ref="A56:A108" si="2">A55+1</f>
         <v>55</v>
@@ -20988,7 +20991,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="57" spans="1:39" ht="40.799999999999997" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:39" ht="45" x14ac:dyDescent="0.25">
       <c r="A57" s="3">
         <f t="shared" si="2"/>
         <v>56</v>
@@ -21106,7 +21109,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="58" spans="1:39" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:39" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A58" s="3">
         <f t="shared" si="2"/>
         <v>57</v>
@@ -21224,7 +21227,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="59" spans="1:39" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:39" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A59" s="3">
         <f t="shared" si="2"/>
         <v>58</v>
@@ -21342,7 +21345,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="60" spans="1:39" ht="40.799999999999997" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:39" ht="45" x14ac:dyDescent="0.25">
       <c r="A60" s="3">
         <f t="shared" si="2"/>
         <v>59</v>
@@ -21460,7 +21463,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="61" spans="1:39" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:39" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A61" s="3">
         <f t="shared" si="2"/>
         <v>60</v>
@@ -21578,7 +21581,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="62" spans="1:39" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:39" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A62" s="3">
         <f t="shared" si="2"/>
         <v>61</v>
@@ -21696,7 +21699,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="63" spans="1:39" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:39" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A63" s="3">
         <f t="shared" si="2"/>
         <v>62</v>
@@ -21814,7 +21817,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="64" spans="1:39" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:39" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A64" s="3">
         <f t="shared" si="2"/>
         <v>63</v>
@@ -21932,7 +21935,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="65" spans="1:39" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:39" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A65" s="3">
         <f t="shared" si="2"/>
         <v>64</v>
@@ -22050,7 +22053,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="66" spans="1:39" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:39" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A66" s="3">
         <f t="shared" si="2"/>
         <v>65</v>
@@ -22168,7 +22171,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="67" spans="1:39" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:39" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A67" s="3">
         <f t="shared" si="2"/>
         <v>66</v>
@@ -22286,7 +22289,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="68" spans="1:39" ht="40.799999999999997" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:39" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A68" s="3">
         <f t="shared" si="2"/>
         <v>67</v>
@@ -22404,7 +22407,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="69" spans="1:39" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:39" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A69" s="3">
         <f t="shared" si="2"/>
         <v>68</v>
@@ -22522,7 +22525,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="70" spans="1:39" ht="40.799999999999997" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:39" ht="45" x14ac:dyDescent="0.25">
       <c r="A70" s="3">
         <f t="shared" si="2"/>
         <v>69</v>
@@ -22640,7 +22643,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="71" spans="1:39" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:39" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A71" s="3">
         <f t="shared" si="2"/>
         <v>70</v>
@@ -22758,7 +22761,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="72" spans="1:39" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:39" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A72" s="3">
         <f t="shared" si="2"/>
         <v>71</v>
@@ -22876,7 +22879,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="73" spans="1:39" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:39" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A73" s="3">
         <f>A72+1</f>
         <v>72</v>
@@ -22994,7 +22997,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="74" spans="1:39" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:39" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A74" s="3">
         <f t="shared" si="2"/>
         <v>73</v>
@@ -23112,7 +23115,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="75" spans="1:39" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:39" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A75" s="3">
         <f t="shared" si="2"/>
         <v>74</v>
@@ -23230,7 +23233,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="76" spans="1:39" ht="40.799999999999997" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:39" ht="45" x14ac:dyDescent="0.25">
       <c r="A76" s="3">
         <f t="shared" si="2"/>
         <v>75</v>
@@ -23348,7 +23351,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="77" spans="1:39" ht="40.799999999999997" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:39" ht="45" x14ac:dyDescent="0.25">
       <c r="A77" s="3">
         <f t="shared" si="2"/>
         <v>76</v>
@@ -23466,7 +23469,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="78" spans="1:39" ht="40.799999999999997" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:39" ht="45" x14ac:dyDescent="0.25">
       <c r="A78" s="3">
         <f t="shared" si="2"/>
         <v>77</v>
@@ -23584,7 +23587,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="79" spans="1:39" ht="40.799999999999997" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:39" ht="45" x14ac:dyDescent="0.25">
       <c r="A79" s="3">
         <f t="shared" si="2"/>
         <v>78</v>
@@ -23702,7 +23705,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="80" spans="1:39" ht="40.799999999999997" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:39" ht="45" x14ac:dyDescent="0.25">
       <c r="A80" s="3">
         <f t="shared" si="2"/>
         <v>79</v>
@@ -23822,7 +23825,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="81" spans="1:39" ht="40.799999999999997" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:39" ht="45" x14ac:dyDescent="0.25">
       <c r="A81" s="3">
         <f t="shared" si="2"/>
         <v>80</v>
@@ -23942,7 +23945,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="82" spans="1:39" ht="51" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:39" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A82" s="3">
         <f t="shared" si="2"/>
         <v>81</v>
@@ -24060,7 +24063,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="83" spans="1:39" ht="51" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:39" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A83" s="3">
         <f t="shared" si="2"/>
         <v>82</v>
@@ -24178,7 +24181,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="84" spans="1:39" ht="40.799999999999997" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:39" ht="45" x14ac:dyDescent="0.25">
       <c r="A84" s="3">
         <f t="shared" si="2"/>
         <v>83</v>
@@ -24296,7 +24299,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="85" spans="1:39" ht="40.799999999999997" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:39" ht="45" x14ac:dyDescent="0.25">
       <c r="A85" s="3">
         <f t="shared" si="2"/>
         <v>84</v>
@@ -24414,7 +24417,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="86" spans="1:39" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:39" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A86" s="3">
         <f t="shared" si="2"/>
         <v>85</v>
@@ -24532,7 +24535,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="87" spans="1:39" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:39" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A87" s="3">
         <f>A86+1</f>
         <v>86</v>
@@ -24650,7 +24653,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="88" spans="1:39" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:39" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A88" s="3">
         <f t="shared" si="2"/>
         <v>87</v>
@@ -24768,7 +24771,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="89" spans="1:39" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:39" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A89" s="3">
         <f t="shared" si="2"/>
         <v>88</v>
@@ -24886,7 +24889,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="90" spans="1:39" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:39" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A90" s="3">
         <f t="shared" si="2"/>
         <v>89</v>
@@ -25004,7 +25007,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="91" spans="1:39" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:39" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A91" s="3">
         <f t="shared" si="2"/>
         <v>90</v>
@@ -25122,7 +25125,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="92" spans="1:39" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:39" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A92" s="3">
         <f t="shared" si="2"/>
         <v>91</v>
@@ -25240,7 +25243,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="93" spans="1:39" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:39" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A93" s="3">
         <f t="shared" si="2"/>
         <v>92</v>
@@ -25358,7 +25361,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="94" spans="1:39" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:39" ht="51" x14ac:dyDescent="0.25">
       <c r="A94" s="3">
         <f>A93+1</f>
         <v>93</v>
@@ -25476,7 +25479,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="95" spans="1:39" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:39" ht="51" x14ac:dyDescent="0.25">
       <c r="A95" s="3">
         <f t="shared" si="2"/>
         <v>94</v>
@@ -25594,7 +25597,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="96" spans="1:39" ht="51" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:39" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A96" s="3">
         <f t="shared" si="2"/>
         <v>95</v>
@@ -25714,7 +25717,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="97" spans="1:39" ht="61.2" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:39" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A97" s="3">
         <f t="shared" si="2"/>
         <v>96</v>
@@ -25834,7 +25837,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="98" spans="1:39" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:39" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A98" s="3">
         <f t="shared" si="2"/>
         <v>97</v>
@@ -25952,7 +25955,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="99" spans="1:39" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:39" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A99" s="3">
         <f t="shared" si="2"/>
         <v>98</v>
@@ -26070,7 +26073,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="100" spans="1:39" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:39" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A100" s="3">
         <f t="shared" si="2"/>
         <v>99</v>
@@ -26188,7 +26191,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="101" spans="1:39" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:39" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A101" s="3">
         <f t="shared" si="2"/>
         <v>100</v>
@@ -26306,7 +26309,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="102" spans="1:39" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:39" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A102" s="3">
         <f t="shared" si="2"/>
         <v>101</v>
@@ -26424,7 +26427,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="103" spans="1:39" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:39" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A103" s="3">
         <f>A102+1</f>
         <v>102</v>
@@ -26542,7 +26545,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="104" spans="1:39" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:39" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A104" s="3">
         <f t="shared" si="2"/>
         <v>103</v>
@@ -26660,7 +26663,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="105" spans="1:39" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:39" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A105" s="3">
         <f t="shared" si="2"/>
         <v>104</v>
@@ -26778,7 +26781,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="106" spans="1:39" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:39" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A106" s="3">
         <f t="shared" si="2"/>
         <v>105</v>
@@ -26896,7 +26899,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="107" spans="1:39" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:39" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A107" s="3">
         <f t="shared" si="2"/>
         <v>106</v>
@@ -27014,7 +27017,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="108" spans="1:39" ht="40.799999999999997" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:39" ht="45" x14ac:dyDescent="0.25">
       <c r="A108" s="3">
         <f t="shared" si="2"/>
         <v>107</v>
@@ -27132,7 +27135,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="109" spans="1:39" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:39" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A109" s="3">
         <f>A108+1</f>
         <v>108</v>
@@ -27260,20 +27263,20 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94559DD8-8EE1-4E67-A709-D32CCBD5C8AB}">
   <dimension ref="A1:AN55"/>
-  <sheetFormatPr defaultRowHeight="10.199999999999999" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="11.25" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.77734375" style="5" customWidth="1"/>
-    <col min="2" max="6" width="10.77734375" style="5" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="7" max="7" width="23.88671875" style="5" customWidth="1" collapsed="1"/>
-    <col min="8" max="18" width="10.77734375" style="5" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="19" max="19" width="5.77734375" style="5" customWidth="1" collapsed="1"/>
-    <col min="20" max="37" width="5.77734375" style="5" customWidth="1"/>
-    <col min="38" max="39" width="10.77734375" style="5" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="40" max="40" width="8.88671875" style="5" collapsed="1"/>
-    <col min="41" max="16384" width="8.88671875" style="5"/>
+    <col min="1" max="1" width="10.7109375" style="5" customWidth="1"/>
+    <col min="2" max="6" width="10.7109375" style="5" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="7" max="7" width="23.85546875" style="5" customWidth="1" collapsed="1"/>
+    <col min="8" max="18" width="10.7109375" style="5" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="19" max="19" width="5.7109375" style="5" customWidth="1" collapsed="1"/>
+    <col min="20" max="37" width="5.7109375" style="5" customWidth="1"/>
+    <col min="38" max="39" width="10.7109375" style="5" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="40" max="40" width="8.85546875" style="5" collapsed="1"/>
+    <col min="41" max="16384" width="8.85546875" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39" s="2" customFormat="1" ht="40.799999999999997" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:39" s="2" customFormat="1" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -27392,7 +27395,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:39" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:39" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -27494,7 +27497,7 @@
       <c r="AL2" s="4"/>
       <c r="AM2" s="4"/>
     </row>
-    <row r="3" spans="1:39" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:39" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <f>A2+1</f>
         <v>2</v>
@@ -27597,7 +27600,7 @@
       <c r="AL3" s="4"/>
       <c r="AM3" s="4"/>
     </row>
-    <row r="4" spans="1:39" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:39" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <f>A3+1</f>
         <v>3</v>
@@ -27700,7 +27703,7 @@
       <c r="AL4" s="4"/>
       <c r="AM4" s="4"/>
     </row>
-    <row r="5" spans="1:39" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:39" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <f t="shared" ref="A5:A30" si="0">A4+1</f>
         <v>4</v>
@@ -27803,7 +27806,7 @@
       <c r="AL5" s="4"/>
       <c r="AM5" s="4"/>
     </row>
-    <row r="6" spans="1:39" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:39" ht="51" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -27906,7 +27909,7 @@
       <c r="AL6" s="4"/>
       <c r="AM6" s="4"/>
     </row>
-    <row r="7" spans="1:39" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:39" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -28009,7 +28012,7 @@
       <c r="AL7" s="4"/>
       <c r="AM7" s="4"/>
     </row>
-    <row r="8" spans="1:39" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:39" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -28112,7 +28115,7 @@
       <c r="AL8" s="4"/>
       <c r="AM8" s="4"/>
     </row>
-    <row r="9" spans="1:39" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:39" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -28215,7 +28218,7 @@
       <c r="AL9" s="4"/>
       <c r="AM9" s="4"/>
     </row>
-    <row r="10" spans="1:39" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:39" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -28318,7 +28321,7 @@
       <c r="AL10" s="4"/>
       <c r="AM10" s="4"/>
     </row>
-    <row r="11" spans="1:39" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:39" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -28421,7 +28424,7 @@
       <c r="AL11" s="4"/>
       <c r="AM11" s="4"/>
     </row>
-    <row r="12" spans="1:39" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:39" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -28524,7 +28527,7 @@
       <c r="AL12" s="4"/>
       <c r="AM12" s="4"/>
     </row>
-    <row r="13" spans="1:39" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:39" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -28627,7 +28630,7 @@
       <c r="AL13" s="4"/>
       <c r="AM13" s="4"/>
     </row>
-    <row r="14" spans="1:39" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:39" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -28730,7 +28733,7 @@
       <c r="AL14" s="4"/>
       <c r="AM14" s="4"/>
     </row>
-    <row r="15" spans="1:39" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:39" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -28833,7 +28836,7 @@
       <c r="AL15" s="4"/>
       <c r="AM15" s="4"/>
     </row>
-    <row r="16" spans="1:39" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:39" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -28936,7 +28939,7 @@
       <c r="AL16" s="4"/>
       <c r="AM16" s="4"/>
     </row>
-    <row r="17" spans="1:39" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:39" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -29039,7 +29042,7 @@
       <c r="AL17" s="4"/>
       <c r="AM17" s="4"/>
     </row>
-    <row r="18" spans="1:39" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:39" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -29142,7 +29145,7 @@
       <c r="AL18" s="4"/>
       <c r="AM18" s="4"/>
     </row>
-    <row r="19" spans="1:39" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:39" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -29245,7 +29248,7 @@
       <c r="AL19" s="4"/>
       <c r="AM19" s="4"/>
     </row>
-    <row r="20" spans="1:39" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:39" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -29348,7 +29351,7 @@
       <c r="AL20" s="4"/>
       <c r="AM20" s="4"/>
     </row>
-    <row r="21" spans="1:39" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:39" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -29451,7 +29454,7 @@
       <c r="AL21" s="4"/>
       <c r="AM21" s="4"/>
     </row>
-    <row r="22" spans="1:39" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:39" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -29554,7 +29557,7 @@
       <c r="AL22" s="4"/>
       <c r="AM22" s="4"/>
     </row>
-    <row r="23" spans="1:39" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:39" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -29657,7 +29660,7 @@
       <c r="AL23" s="4"/>
       <c r="AM23" s="4"/>
     </row>
-    <row r="24" spans="1:39" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:39" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -29760,7 +29763,7 @@
       <c r="AL24" s="4"/>
       <c r="AM24" s="4"/>
     </row>
-    <row r="25" spans="1:39" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:39" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -29863,7 +29866,7 @@
       <c r="AL25" s="4"/>
       <c r="AM25" s="4"/>
     </row>
-    <row r="26" spans="1:39" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:39" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -29966,7 +29969,7 @@
       <c r="AL26" s="4"/>
       <c r="AM26" s="4"/>
     </row>
-    <row r="27" spans="1:39" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:39" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -30069,7 +30072,7 @@
       <c r="AL27" s="4"/>
       <c r="AM27" s="4"/>
     </row>
-    <row r="28" spans="1:39" ht="66" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:39" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <f>A27+1</f>
         <v>27</v>
@@ -30172,7 +30175,7 @@
       <c r="AL28" s="4"/>
       <c r="AM28" s="4"/>
     </row>
-    <row r="29" spans="1:39" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:39" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -30275,7 +30278,7 @@
       <c r="AL29" s="4"/>
       <c r="AM29" s="4"/>
     </row>
-    <row r="30" spans="1:39" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:39" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -30378,7 +30381,7 @@
       <c r="AL30" s="4"/>
       <c r="AM30" s="4"/>
     </row>
-    <row r="31" spans="1:39" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:39" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <f>A30+1</f>
         <v>30</v>
@@ -30481,7 +30484,7 @@
       <c r="AL31" s="4"/>
       <c r="AM31" s="4"/>
     </row>
-    <row r="32" spans="1:39" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:39" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <f t="shared" ref="A32:A54" si="1">A31+1</f>
         <v>31</v>
@@ -30584,7 +30587,7 @@
       <c r="AL32" s="4"/>
       <c r="AM32" s="4"/>
     </row>
-    <row r="33" spans="1:39" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:39" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <f t="shared" si="1"/>
         <v>32</v>
@@ -30687,7 +30690,7 @@
       <c r="AL33" s="4"/>
       <c r="AM33" s="4"/>
     </row>
-    <row r="34" spans="1:39" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:39" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <f t="shared" si="1"/>
         <v>33</v>
@@ -30790,7 +30793,7 @@
       <c r="AL34" s="4"/>
       <c r="AM34" s="4"/>
     </row>
-    <row r="35" spans="1:39" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:39" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <f t="shared" si="1"/>
         <v>34</v>
@@ -30893,7 +30896,7 @@
       <c r="AL35" s="4"/>
       <c r="AM35" s="4"/>
     </row>
-    <row r="36" spans="1:39" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:39" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <f t="shared" si="1"/>
         <v>35</v>
@@ -30996,7 +30999,7 @@
       <c r="AL36" s="4"/>
       <c r="AM36" s="4"/>
     </row>
-    <row r="37" spans="1:39" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:39" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
         <f t="shared" si="1"/>
         <v>36</v>
@@ -31099,7 +31102,7 @@
       <c r="AL37" s="4"/>
       <c r="AM37" s="4"/>
     </row>
-    <row r="38" spans="1:39" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:39" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
         <f t="shared" si="1"/>
         <v>37</v>
@@ -31202,7 +31205,7 @@
       <c r="AL38" s="4"/>
       <c r="AM38" s="4"/>
     </row>
-    <row r="39" spans="1:39" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:39" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
         <f t="shared" si="1"/>
         <v>38</v>
@@ -31305,7 +31308,7 @@
       <c r="AL39" s="4"/>
       <c r="AM39" s="4"/>
     </row>
-    <row r="40" spans="1:39" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:39" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
         <f t="shared" si="1"/>
         <v>39</v>
@@ -31408,7 +31411,7 @@
       <c r="AL40" s="4"/>
       <c r="AM40" s="4"/>
     </row>
-    <row r="41" spans="1:39" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:39" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
         <f t="shared" si="1"/>
         <v>40</v>
@@ -31511,7 +31514,7 @@
       <c r="AL41" s="4"/>
       <c r="AM41" s="4"/>
     </row>
-    <row r="42" spans="1:39" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:39" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
         <f t="shared" si="1"/>
         <v>41</v>
@@ -31614,7 +31617,7 @@
       <c r="AL42" s="4"/>
       <c r="AM42" s="4"/>
     </row>
-    <row r="43" spans="1:39" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:39" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
         <f t="shared" si="1"/>
         <v>42</v>
@@ -31717,7 +31720,7 @@
       <c r="AL43" s="4"/>
       <c r="AM43" s="4"/>
     </row>
-    <row r="44" spans="1:39" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:39" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
         <f t="shared" si="1"/>
         <v>43</v>
@@ -31820,7 +31823,7 @@
       <c r="AL44" s="4"/>
       <c r="AM44" s="4"/>
     </row>
-    <row r="45" spans="1:39" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:39" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
         <f t="shared" si="1"/>
         <v>44</v>
@@ -31923,7 +31926,7 @@
       <c r="AL45" s="4"/>
       <c r="AM45" s="4"/>
     </row>
-    <row r="46" spans="1:39" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:39" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
         <f t="shared" si="1"/>
         <v>45</v>
@@ -32026,7 +32029,7 @@
       <c r="AL46" s="4"/>
       <c r="AM46" s="4"/>
     </row>
-    <row r="47" spans="1:39" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:39" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <f t="shared" si="1"/>
         <v>46</v>
@@ -32129,7 +32132,7 @@
       <c r="AL47" s="4"/>
       <c r="AM47" s="4"/>
     </row>
-    <row r="48" spans="1:39" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:39" ht="51" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <f t="shared" si="1"/>
         <v>47</v>
@@ -32232,7 +32235,7 @@
       <c r="AL48" s="4"/>
       <c r="AM48" s="4"/>
     </row>
-    <row r="49" spans="1:39" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:39" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
         <f t="shared" si="1"/>
         <v>48</v>
@@ -32335,7 +32338,7 @@
       <c r="AL49" s="4"/>
       <c r="AM49" s="4"/>
     </row>
-    <row r="50" spans="1:39" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:39" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
         <f t="shared" si="1"/>
         <v>49</v>
@@ -32381,7 +32384,7 @@
       <c r="AL50" s="4"/>
       <c r="AM50" s="4"/>
     </row>
-    <row r="51" spans="1:39" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:39" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
         <f>A50+1</f>
         <v>50</v>
@@ -32484,7 +32487,7 @@
       <c r="AL51" s="4"/>
       <c r="AM51" s="4"/>
     </row>
-    <row r="52" spans="1:39" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:39" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
         <f t="shared" si="1"/>
         <v>51</v>
@@ -32587,7 +32590,7 @@
       <c r="AL52" s="4"/>
       <c r="AM52" s="4"/>
     </row>
-    <row r="53" spans="1:39" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:39" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
         <f t="shared" si="1"/>
         <v>52</v>
@@ -32690,7 +32693,7 @@
       <c r="AL53" s="4"/>
       <c r="AM53" s="4"/>
     </row>
-    <row r="54" spans="1:39" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:39" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
         <f t="shared" si="1"/>
         <v>53</v>
@@ -32793,7 +32796,7 @@
       <c r="AL54" s="4"/>
       <c r="AM54" s="4"/>
     </row>
-    <row r="55" spans="1:39" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:39" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A55" s="3">
         <f>A54+1</f>
         <v>54</v>

--- a/saad-digital-marketing/data/saad-digi-marketing-dta.xlsx
+++ b/saad-digital-marketing/data/saad-digi-marketing-dta.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\viser\OneDrive\Dokumen\Github repository\data-consultation-2026\saad-digital-marketing\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D08DCF22-2150-4D87-B170-2C64C4EFCECF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAEBCCB4-2E91-40EB-A56D-569D1F154D0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{6C9933B8-D739-4C2C-BD08-E89F383740DE}"/>
+    <workbookView xWindow="30330" yWindow="1785" windowWidth="21600" windowHeight="11835" activeTab="1" xr2:uid="{6C9933B8-D739-4C2C-BD08-E89F383740DE}"/>
   </bookViews>
   <sheets>
     <sheet name="raw_data" sheetId="4" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4143" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4143" uniqueCount="304">
   <si>
     <t>Respondent No.</t>
   </si>
@@ -948,6 +948,12 @@
   <si>
     <t>Limited government support</t>
   </si>
+  <si>
+    <t xml:space="preserve">Our enterprise has limited access to smartphones or digital devices needed for digital marketing. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Our enterprise uses digital platforms or online channels to support product ordering or sales transactions.  </t>
+  </si>
 </sst>
 </file>
 
@@ -14153,7 +14159,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="s">
-        <v>281</v>
+        <v>302</v>
       </c>
       <c r="B3" s="16" t="s">
         <v>9</v>
@@ -14340,7 +14346,7 @@
     </row>
     <row r="20" spans="1:3" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="B20" s="16" t="s">
         <v>26</v>
